--- a/Results/Summary.xlsx
+++ b/Results/Summary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://biu365-my.sharepoint.com/personal/samoily_biu_ac_il/Documents/Academic/Postdoc/Multiplexed analyses/IMC/Scripts/Results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://biu365-my.sharepoint.com/personal/samoily_biu_ac_il/Documents/Academic/Postdoc/Multiplexed analyses/IMC/Results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="11_F25DC773A252ABDACC1048A339584C225BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32D97788-91E6-48B2-A05F-42084AB74B6C}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="11_F25DC773A252ABDACC1048A339584C225BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE0F97BF-9324-472F-B68F-1A3F32CB654E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="32">
   <si>
     <t>Dataset</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>C45</t>
+  </si>
+  <si>
+    <t>avg</t>
   </si>
 </sst>
 </file>
@@ -12035,11 +12038,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="20.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12970,7 +12973,7 @@
         <v>20</v>
       </c>
       <c r="D79" s="4">
-        <f t="shared" ref="D79:D88" si="1">VLOOKUP(B79,$B$46:$D$56,3,0)</f>
+        <f t="shared" ref="D79:D87" si="1">VLOOKUP(B79,$B$46:$D$56,3,0)</f>
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
@@ -12983,7 +12986,7 @@
         <v>0.21759999999999999</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>19</v>
       </c>
@@ -12992,7 +12995,7 @@
         <v>0.37040000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>21</v>
       </c>
@@ -13001,7 +13004,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>6</v>
       </c>
@@ -13010,7 +13013,7 @@
         <v>0.57399999999999995</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>7</v>
       </c>
@@ -13019,7 +13022,7 @@
         <v>8.0799999999999997E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>8</v>
       </c>
@@ -13028,7 +13031,7 @@
         <v>0.36820000000000003</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>9</v>
       </c>
@@ -13037,7 +13040,7 @@
         <v>0.17499999999999999</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>10</v>
       </c>
@@ -13046,16 +13049,29 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>11</v>
       </c>
       <c r="D88" s="4">
-        <f t="shared" si="1"/>
+        <f>VLOOKUP(B88,$B$46:$D$56,3,0)</f>
         <v>0.57750000000000001</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C90" t="s">
+        <v>31</v>
+      </c>
+      <c r="D90" s="4">
+        <f>AVERAGE(D77:D88)</f>
+        <v>0.28969090909090911</v>
+      </c>
+      <c r="E90" s="4">
+        <f>_xlfn.STDEV.P(D78:D88)/SQRT(COUNT(D78:D88))</f>
+        <v>5.3580742276494009E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>28</v>
       </c>
@@ -13071,7 +13087,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>20</v>
       </c>
@@ -13084,7 +13100,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>17</v>
       </c>
@@ -13206,6 +13222,9 @@
         <f t="shared" si="2"/>
         <v>166.5</v>
       </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D105" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A45:G45" xr:uid="{00000000-0001-0000-0000-000000000000}">

--- a/Results/Summary.xlsx
+++ b/Results/Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://biu365-my.sharepoint.com/personal/samoily_biu_ac_il/Documents/Academic/Postdoc/Multiplexed analyses/IMC/Results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="166" documentId="11_F25DC773A252ABDACC1048A339584C225BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE0F97BF-9324-472F-B68F-1A3F32CB654E}"/>
+  <xr:revisionPtr revIDLastSave="260" documentId="11_F25DC773A252ABDACC1048A339584C225BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76B7E37F-F0F2-4F43-BA78-0195C7DCEC3F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="37">
   <si>
     <t>Dataset</t>
   </si>
@@ -135,7 +135,22 @@
     <t>C45</t>
   </si>
   <si>
-    <t>avg</t>
+    <t>J2D + PCA</t>
+  </si>
+  <si>
+    <t>avg corr</t>
+  </si>
+  <si>
+    <t>ΔPCA</t>
+  </si>
+  <si>
+    <t>J2D - no PCA</t>
+  </si>
+  <si>
+    <t>ΔPCA + Frozen conv1</t>
+  </si>
+  <si>
+    <t>J2D + PCA + Frozen conv1</t>
   </si>
 </sst>
 </file>
@@ -175,12 +190,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -544,153 +562,169 @@
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="3"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$32</c:f>
+              <c:f>Sheet1!$F$77</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>D - % area</c:v>
+                  <c:v>J2D + PCA + Frozen conv1</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:noFill/>
+            <a:solidFill>
+              <a:srgbClr val="92D050"/>
+            </a:solidFill>
             <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$94:$B$104</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="11"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>CD3</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>CD68</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>CD20</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>CD45</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>sma</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Pan-CK</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>CK5</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>CK8-18</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>Ki67</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>HER2</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>ERa</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Immune</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Identity</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>Clinical</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$94:$C$104</c:f>
+              <c:f>Sheet1!$F$94:$F$104</c:f>
               <c:numCache>
-                <c:formatCode>0</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>9.5516059779999996</c:v>
+                  <c:v>335.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>34.598979030000002</c:v>
+                  <c:v>371.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.2566599309999997</c:v>
+                  <c:v>307.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.76826843</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>66.19802722</c:v>
+                  <c:v>187.85</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.00">
+                  <c:v>208.06</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13.486557269999999</c:v>
+                  <c:v>223.67</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>14.58223203</c:v>
+                  <c:v>345.61</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>61.985700940000001</c:v>
+                  <c:v>223.14</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38.822217160000001</c:v>
+                  <c:v>274.22000000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>40.82876701</c:v>
+                  <c:v>170.05</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.1747951170000004</c:v>
+                  <c:v>201.57</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3A0D-4632-9F6D-E582F1EAE94B}"/>
+              <c16:uniqueId val="{00000001-616A-4D55-AD9F-871EEED13386}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>J2D - no PCA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$94:$E$104</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>320.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>282.99</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>270.92</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>167.42</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>195.12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>263.81</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>378.26</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>226.95</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>261.54000000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>205.73</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>209.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E6B0-4838-A5E9-4E786294BD7E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
-          <c:order val="1"/>
+          <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$32</c:f>
+              <c:f>Sheet1!$D$77</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>J2D</c:v>
+                  <c:v>J2D + PCA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="tx2"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -808,6 +842,7 @@
         <c:gapWidth val="182"/>
         <c:axId val="450038527"/>
         <c:axId val="450038943"/>
+        <c:extLst/>
       </c:barChart>
       <c:catAx>
         <c:axId val="450038527"/>
@@ -835,7 +870,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -872,7 +907,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -885,8 +920,8 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1800"/>
-                  <a:t>FID</a:t>
+                  <a:rPr lang="en-US"/>
+                  <a:t>FID (lower is better)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -904,7 +939,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -938,7 +973,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -966,51 +1001,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.68285069169575829"/>
-          <c:y val="4.0450012784454092E-2"/>
-          <c:w val="0.1850150494211906"/>
-          <c:h val="0.19703657135864602"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="LID4096"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1030,7 +1020,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr sz="1400"/>
+        <a:defRPr sz="1600"/>
       </a:pPr>
       <a:endParaRPr lang="LID4096"/>
     </a:p>
@@ -1556,6 +1546,1715 @@
     <c:pageSetup/>
   </c:printSettings>
   <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14730656532331199"/>
+          <c:y val="4.8198723648115505E-2"/>
+          <c:w val="0.8092420285807217"/>
+          <c:h val="0.78251656593195784"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$H$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ΔPCA + Frozen conv1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$78:$B$88</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>CD3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>CD68</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>CD20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>CD45</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>sma</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Pan-CK</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>CK5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>CK8-18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Ki67</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>HER2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>ERa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$78:$H$88</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-1.5300000000000008E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-6.4399999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.2200000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2.0999999999999908E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.6000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.45199999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-2.0000000000000018E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-8.5999999999999965E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.8699999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.9300000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-3.1299999999999994E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-132C-4226-960C-02037EE88B84}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ΔPCA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$78:$B$88</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>CD3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>CD68</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>CD20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>CD45</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>sma</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Pan-CK</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>CK5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>CK8-18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Ki67</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>HER2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>ERa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$78:$G$88</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-2.8999999999999859E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9599999999999987E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.5600000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.10400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.43899999999999995</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.7999999999999969E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-2.579999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.3999999999999987E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.5000000000000031E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-8.499999999999952E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-5A07-40DE-8B80-8949FE9713C7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="450038527"/>
+        <c:axId val="450038943"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="450038527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="450038943"/>
+        <c:crossesAt val="0"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="450038943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.5"/>
+          <c:min val="-0.5"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="el-GR"/>
+                  <a:t>Δ</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t> corr.</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="LID4096"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="450038527"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="0.2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.8245354016499954E-2"/>
+          <c:y val="0.60895336144740653"/>
+          <c:w val="0.41186801170226772"/>
+          <c:h val="0.20524605637540974"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="LID4096"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1600"/>
+      </a:pPr>
+      <a:endParaRPr lang="LID4096"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13586383175358807"/>
+          <c:y val="4.8198723648115505E-2"/>
+          <c:w val="0.82068487737219653"/>
+          <c:h val="0.78251656593195784"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$H$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ΔPCA + Frozen conv1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$94:$B$104</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>CD3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>CD68</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>CD20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>CD45</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>sma</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Pan-CK</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>CK5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>CK8-18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Ki67</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>HER2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>ERa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$94:$H$104</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>15.100000000000023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>88.70999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36.879999999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.430000000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12.939999999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-40.140000000000015</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-32.649999999999977</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-3.8100000000000023</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12.680000000000007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-35.679999999999978</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-7.6800000000000068</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-597C-4E20-BD4D-2A4200B43EC5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ΔPCA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$94:$B$104</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>CD3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>CD68</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>CD20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>CD45</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>sma</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Pan-CK</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>CK5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>CK8-18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Ki67</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>HER2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>ERa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$94:$G$104</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>78.009999999999991</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80.079999999999984</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38.580000000000013</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-8.2199999999999989</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-65.81</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-41.259999999999991</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-37.349999999999994</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.4599999999999795</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-44.22999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-42.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-5454-4BC8-94B5-D90B583F8692}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="450038527"/>
+        <c:axId val="450038943"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="450038527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="450038943"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="450038943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="el-GR"/>
+                  <a:t>Δ</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t> FID</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="LID4096"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="450038527"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="100"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1600"/>
+      </a:pPr>
+      <a:endParaRPr lang="LID4096"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13586383175358807"/>
+          <c:y val="4.8198723648115505E-2"/>
+          <c:w val="0.82068487737219653"/>
+          <c:h val="0.78251656593195784"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$32</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>D - % area</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="LID4096"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$A$94:$B$104</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="11"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>CD3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>CD68</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>CD20</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>CD45</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Pan-CK</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>CK5</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>CK8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Ki67</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Identity</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$94:$C$104</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>9.5516059779999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>34.598979030000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.2566599309999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.76826843</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>66.19802722</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13.486557269999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14.58223203</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>61.985700940000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38.822217160000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>40.82876701</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.1747951170000004</c:v>
+                </c:pt>
+              </c:numCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:val>
+          <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-67C0-47D0-AF1D-8E460762805A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="450038527"/>
+        <c:axId val="450038943"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$E$77</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>J2D - no PCA</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="bg1">
+                      <a:lumMod val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$E$94:$E$104</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="11"/>
+                      <c:pt idx="0">
+                        <c:v>320.5</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>282.99</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>270.92</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>167.42</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>195.12</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>263.81</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>378.26</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>226.95</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>261.54000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>205.73</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>209.25</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-67C0-47D0-AF1D-8E460762805A}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$D$77</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>J2D + PCA</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$94:$B$104</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="11"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>CD3</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>CD68</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>CD20</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>CD45</c:v>
+                        </c:pt>
+                        <c:pt idx="4">
+                          <c:v>sma</c:v>
+                        </c:pt>
+                        <c:pt idx="5">
+                          <c:v>Pan-CK</c:v>
+                        </c:pt>
+                        <c:pt idx="6">
+                          <c:v>CK5</c:v>
+                        </c:pt>
+                        <c:pt idx="7">
+                          <c:v>CK8-18</c:v>
+                        </c:pt>
+                        <c:pt idx="8">
+                          <c:v>Ki67</c:v>
+                        </c:pt>
+                        <c:pt idx="9">
+                          <c:v>HER2</c:v>
+                        </c:pt>
+                        <c:pt idx="10">
+                          <c:v>ERa</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>Immune</c:v>
+                        </c:pt>
+                        <c:pt idx="4">
+                          <c:v>Identity</c:v>
+                        </c:pt>
+                        <c:pt idx="8">
+                          <c:v>Clinical</c:v>
+                        </c:pt>
+                      </c:lvl>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$D$94:$D$104</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.0</c:formatCode>
+                      <c:ptCount val="11"/>
+                      <c:pt idx="0">
+                        <c:v>346</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>361</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>351</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>206</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>186.9</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>198</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>337</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>189.6</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>263</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>161.5</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>166.5</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-67C0-47D0-AF1D-8E460762805A}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$F$77</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>J2D + PCA + Frozen conv1</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:srgbClr val="92D050"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$F$94:$F$104</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="11"/>
+                      <c:pt idx="0">
+                        <c:v>335.6</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>371.7</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>307.8</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>187.85</c:v>
+                      </c:pt>
+                      <c:pt idx="4" formatCode="0.00">
+                        <c:v>208.06</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>223.67</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>345.61</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>223.14</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>274.22000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>170.05</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>201.57</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-67C0-47D0-AF1D-8E460762805A}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="450038527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="450038943"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="450038943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1800"/>
+                  <a:t>% raw area covered</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="LID4096"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="450038527"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="25"/>
+        <c:minorUnit val="25"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1400"/>
+      </a:pPr>
+      <a:endParaRPr lang="LID4096"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
@@ -4861,10 +6560,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.14730656532331199"/>
-          <c:y val="4.8198723648115505E-2"/>
+          <c:x val="0.19226655399373865"/>
+          <c:y val="1.8394128161786191E-2"/>
           <c:w val="0.8092420285807217"/>
-          <c:h val="0.78251656593195784"/>
+          <c:h val="0.82350501489426831"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -4872,22 +6571,22 @@
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="1"/>
+          <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$32</c:f>
+              <c:f>Sheet1!$E$77</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>J2D</c:v>
+                  <c:v>J2D - no PCA</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="tx2"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -4895,109 +6594,317 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="LID4096"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
           <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$B$78:$B$88</c:f>
-              <c:strCache>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$A$94:$B$104</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="11"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>CD3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>CD68</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>CD20</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>CD45</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Pan-CK</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>CK5</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>CK8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Ki67</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Identity</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$78:$E$88</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>CD3</c:v>
+                  <c:v>0.15</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>CD68</c:v>
+                  <c:v>0.16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>CD20</c:v>
+                  <c:v>0.188</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>CD45</c:v>
+                  <c:v>0.38600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>sma</c:v>
+                  <c:v>2.5999999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Pan-CK</c:v>
+                  <c:v>0.13500000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>CK5</c:v>
+                  <c:v>7.8E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>CK8-18</c:v>
+                  <c:v>0.39400000000000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Ki67</c:v>
+                  <c:v>0.111</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>HER2</c:v>
+                  <c:v>0.41499999999999998</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>ERa</c:v>
+                  <c:v>0.58599999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8B98-48E2-A025-73C7EDC32719}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>J2D + PCA + Frozen conv1</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="92D050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$A$94:$B$104</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="11"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>CD3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>CD68</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>CD20</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>CD45</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Pan-CK</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>CK5</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>CK8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Ki67</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Identity</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$78:$F$88</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.13469999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.5600000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.22020000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.38390000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.58699999999999997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.38540000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.1497</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.45429999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.55469999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-51E3-44FD-9875-BE5693CA14EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>J2D + PCA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$A$94:$B$104</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="11"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>CD3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>CD68</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>CD20</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>CD45</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Pan-CK</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>CK5</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>CK8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Ki67</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Identity</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Sheet1!$D$78:$D$88</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0.14710000000000001</c:v>
@@ -5061,14 +6968,14 @@
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -5079,7 +6986,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -5116,7 +7023,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -5130,13 +7037,8 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Correlation</a:t>
+                  <a:t>Pearson's corr.</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> of real and predicted</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -5153,7 +7055,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -5187,7 +7089,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -5215,6 +7117,47 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.58113639061461198"/>
+          <c:y val="0.49740609742409458"/>
+          <c:w val="0.40051121570329662"/>
+          <c:h val="0.32701807882257833"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="LID4096"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -5234,7 +7177,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr sz="1400"/>
+        <a:defRPr sz="1600"/>
       </a:pPr>
       <a:endParaRPr lang="LID4096"/>
     </a:p>
@@ -5328,6 +7271,126 @@
 </file>
 
 <file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -7202,6 +9265,1521 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
@@ -11284,14 +14862,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>347383</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>118783</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>118393</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>47999</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>403599</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>120837</xdr:rowOff>
     </xdr:to>
@@ -11320,14 +14898,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>97915</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>453515</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>117245</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>145142</xdr:colOff>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>500742</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>38904</xdr:rowOff>
     </xdr:to>
@@ -11360,14 +14938,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>582085</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>3486</xdr:rowOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>76759</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>286747</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>181054</xdr:rowOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>58942</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11398,14 +14976,14 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>18900</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>152409</xdr:rowOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>30298</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>112297</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>147490</xdr:rowOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>25378</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11548,16 +15126,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>263323</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>543350</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>46837</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>357476</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>148035</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>305287</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>12309</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11586,16 +15164,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>39933</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>8295</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>313204</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>173787</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>354133</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>653</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11624,16 +15202,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>529167</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>176334</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>138398</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>103065</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>321143</xdr:colOff>
-      <xdr:row>138</xdr:row>
-      <xdr:rowOff>177764</xdr:rowOff>
+      <xdr:colOff>540951</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>104495</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11655,6 +15233,120 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>120478</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>214630</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>117874</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="14" name="Chart 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C183D8C3-549F-4BF5-B26C-10C8BBF49583}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>192129</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>84831</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>293006</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>83539</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="18" name="Chart 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32B662B2-B02A-4E40-B9A2-BE18F3F6C5D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>100878</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>17758</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="17" name="Chart 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C654962-07E1-485F-82F7-0EDB58F1ED33}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -12038,12 +15730,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="20.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -12903,7 +16598,7 @@
         <v>189.6</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
         <v>19</v>
       </c>
@@ -12915,7 +16610,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>10</v>
       </c>
@@ -12927,7 +16622,7 @@
         <v>161.5</v>
       </c>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
         <v>6</v>
       </c>
@@ -12939,7 +16634,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
         <v>11</v>
       </c>
@@ -12951,127 +16646,319 @@
         <v>166.5</v>
       </c>
     </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>16</v>
+        <v>31</v>
+      </c>
+      <c r="E77" t="s">
+        <v>34</v>
+      </c>
+      <c r="F77" t="s">
+        <v>36</v>
+      </c>
+      <c r="G77" t="s">
+        <v>33</v>
+      </c>
+      <c r="H77" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>18</v>
       </c>
-      <c r="D78" s="4">
-        <f>VLOOKUP(B78,$B$46:$D$56,3,0)</f>
+      <c r="D78" s="1">
         <v>0.14710000000000001</v>
       </c>
+      <c r="E78" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="F78" s="6">
+        <v>0.13469999999999999</v>
+      </c>
+      <c r="G78" s="4">
+        <f>D78-E78</f>
+        <v>-2.8999999999999859E-3</v>
+      </c>
+      <c r="H78" s="4">
+        <f>IF(F78&lt;&gt;"",F78-E78, 0)</f>
+        <v>-1.5300000000000008E-2</v>
+      </c>
     </row>
-    <row r="79" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>20</v>
       </c>
-      <c r="D79" s="4">
-        <f t="shared" ref="D79:D87" si="1">VLOOKUP(B79,$B$46:$D$56,3,0)</f>
+      <c r="D79" s="1">
         <v>9.6000000000000002E-2</v>
       </c>
+      <c r="E79" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="F79" s="6">
+        <v>9.5600000000000004E-2</v>
+      </c>
+      <c r="G79" s="4">
+        <f t="shared" ref="G79:G88" si="1">D79-E79</f>
+        <v>-6.4000000000000001E-2</v>
+      </c>
+      <c r="H79" s="4">
+        <f>IF(F79&lt;&gt;"",F79-E79, 0)</f>
+        <v>-6.4399999999999999E-2</v>
+      </c>
     </row>
-    <row r="80" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>17</v>
       </c>
-      <c r="D80" s="4">
+      <c r="D80" s="1">
+        <v>0.21759999999999999</v>
+      </c>
+      <c r="E80" s="1">
+        <v>0.188</v>
+      </c>
+      <c r="F80" s="6">
+        <v>0.22020000000000001</v>
+      </c>
+      <c r="G80" s="4">
         <f t="shared" si="1"/>
-        <v>0.21759999999999999</v>
+        <v>2.9599999999999987E-2</v>
+      </c>
+      <c r="H80" s="4">
+        <f t="shared" ref="H80:H88" si="2">IF(F80&lt;&gt;"",F80-E80, 0)</f>
+        <v>3.2200000000000006E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>19</v>
       </c>
-      <c r="D81" s="4">
+      <c r="D81" s="1">
+        <v>0.37040000000000001</v>
+      </c>
+      <c r="E81" s="6">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="F81" s="6">
+        <v>0.38390000000000002</v>
+      </c>
+      <c r="G81" s="4">
         <f t="shared" si="1"/>
-        <v>0.37040000000000001</v>
+        <v>-1.5600000000000003E-2</v>
+      </c>
+      <c r="H81" s="4">
+        <f t="shared" si="2"/>
+        <v>-2.0999999999999908E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>21</v>
       </c>
-      <c r="D82" s="4">
+      <c r="D82" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="E82" s="6">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="F82" s="6">
+        <v>6.2E-2</v>
+      </c>
+      <c r="G82" s="4">
         <f t="shared" si="1"/>
-        <v>0.13</v>
+        <v>0.10400000000000001</v>
+      </c>
+      <c r="H82" s="4">
+        <f t="shared" si="2"/>
+        <v>3.6000000000000004E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>6</v>
       </c>
-      <c r="D83" s="4">
+      <c r="D83" s="1">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="E83" s="6">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="F83" s="6">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="G83" s="4">
         <f t="shared" si="1"/>
-        <v>0.57399999999999995</v>
+        <v>0.43899999999999995</v>
+      </c>
+      <c r="H83" s="4">
+        <f t="shared" si="2"/>
+        <v>0.45199999999999996</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>7</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D84" s="1">
+        <v>8.0799999999999997E-2</v>
+      </c>
+      <c r="E84" s="6">
+        <v>7.8E-2</v>
+      </c>
+      <c r="F84" s="6">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="G84" s="4">
         <f t="shared" si="1"/>
-        <v>8.0799999999999997E-2</v>
+        <v>2.7999999999999969E-3</v>
+      </c>
+      <c r="H84" s="4">
+        <f t="shared" si="2"/>
+        <v>-2.0000000000000018E-3</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>8</v>
       </c>
-      <c r="D85" s="4">
+      <c r="D85" s="1">
+        <v>0.36820000000000003</v>
+      </c>
+      <c r="E85" s="1">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="F85" s="6">
+        <v>0.38540000000000002</v>
+      </c>
+      <c r="G85" s="4">
         <f t="shared" si="1"/>
-        <v>0.36820000000000003</v>
+        <v>-2.579999999999999E-2</v>
+      </c>
+      <c r="H85" s="4">
+        <f t="shared" si="2"/>
+        <v>-8.5999999999999965E-3</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>9</v>
       </c>
-      <c r="D86" s="4">
+      <c r="D86" s="1">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="E86" s="1">
+        <v>0.111</v>
+      </c>
+      <c r="F86" s="6">
+        <v>0.1497</v>
+      </c>
+      <c r="G86" s="4">
         <f t="shared" si="1"/>
-        <v>0.17499999999999999</v>
+        <v>6.3999999999999987E-2</v>
+      </c>
+      <c r="H86" s="4">
+        <f t="shared" si="2"/>
+        <v>3.8699999999999998E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>10</v>
       </c>
-      <c r="D87" s="4">
+      <c r="D87" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="E87" s="1">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="F87" s="6">
+        <v>0.45429999999999998</v>
+      </c>
+      <c r="G87" s="4">
         <f t="shared" si="1"/>
-        <v>0.45</v>
+        <v>3.5000000000000031E-2</v>
+      </c>
+      <c r="H87" s="4">
+        <f t="shared" si="2"/>
+        <v>3.9300000000000002E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>11</v>
       </c>
-      <c r="D88" s="4">
-        <f>VLOOKUP(B88,$B$46:$D$56,3,0)</f>
+      <c r="D88" s="1">
         <v>0.57750000000000001</v>
       </c>
+      <c r="E88" s="1">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="F88" s="6">
+        <v>0.55469999999999997</v>
+      </c>
+      <c r="G88" s="4">
+        <f t="shared" si="1"/>
+        <v>-8.499999999999952E-3</v>
+      </c>
+      <c r="H88" s="4">
+        <f t="shared" si="2"/>
+        <v>-3.1299999999999994E-2</v>
+      </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C90" t="s">
-        <v>31</v>
-      </c>
-      <c r="D90" s="4">
+        <v>32</v>
+      </c>
+      <c r="D90" s="1">
         <f>AVERAGE(D77:D88)</f>
         <v>0.28969090909090911</v>
       </c>
-      <c r="E90" s="4">
+      <c r="E90" s="1">
+        <f>AVERAGE(E77:E88)</f>
+        <v>0.23899999999999996</v>
+      </c>
+      <c r="F90" s="1">
+        <f>AVERAGE(F77:F88)</f>
+        <v>0.28213636363636363</v>
+      </c>
+      <c r="G90" s="1">
+        <f>AVERAGE(G77:G88)</f>
+        <v>5.0690909090909099E-2</v>
+      </c>
+      <c r="H90" s="1">
+        <f>AVERAGE(H77:H88)</f>
+        <v>4.3136363636363639E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D91" s="4">
         <f>_xlfn.STDEV.P(D78:D88)/SQRT(COUNT(D78:D88))</f>
         <v>5.3580742276494009E-2</v>
       </c>
+      <c r="E91" s="4">
+        <f>_xlfn.STDEV.P(E78:E88)/SQRT(COUNT(E78:E88))</f>
+        <v>5.0801184342281966E-2</v>
+      </c>
+      <c r="F91" s="4">
+        <f>_xlfn.STDEV.P(F78:F88)/SQRT(COUNT(F78:F88))</f>
+        <v>5.6535904298339081E-2</v>
+      </c>
+      <c r="G91" s="4">
+        <f>_xlfn.STDEV.P(G78:G88)/SQRT(COUNT(G78:G88))</f>
+        <v>3.9266246213005965E-2</v>
+      </c>
+      <c r="H91" s="4">
+        <f>_xlfn.STDEV.P(H78:H88)/SQRT(COUNT(H78:H88))</f>
+        <v>4.0108770032358763E-2</v>
+      </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F93" s="5"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>28</v>
       </c>
@@ -13083,11 +16970,24 @@
         <v>9.5516059779999996</v>
       </c>
       <c r="D94" s="2">
-        <f t="shared" ref="D94:D104" si="2">VLOOKUP(B94,$B$58:$D$68,3,0)</f>
         <v>346</v>
       </c>
+      <c r="E94">
+        <v>320.5</v>
+      </c>
+      <c r="F94" s="5">
+        <v>335.6</v>
+      </c>
+      <c r="G94" s="2">
+        <f>D94-E94</f>
+        <v>25.5</v>
+      </c>
+      <c r="H94" s="4">
+        <f>IF(F94&lt;&gt;"",F94-E94, 0)</f>
+        <v>15.100000000000023</v>
+      </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>20</v>
       </c>
@@ -13096,11 +16996,24 @@
         <v>34.598979030000002</v>
       </c>
       <c r="D95" s="2">
-        <f t="shared" si="2"/>
         <v>361</v>
       </c>
+      <c r="E95">
+        <v>282.99</v>
+      </c>
+      <c r="F95" s="5">
+        <v>371.7</v>
+      </c>
+      <c r="G95" s="2">
+        <f t="shared" ref="G95:G104" si="4">D95-E95</f>
+        <v>78.009999999999991</v>
+      </c>
+      <c r="H95" s="4">
+        <f t="shared" ref="H95:H104" si="5">IF(F95&lt;&gt;"",F95-E95, 0)</f>
+        <v>88.70999999999998</v>
+      </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>17</v>
       </c>
@@ -13109,11 +17022,24 @@
         <v>3.2566599309999997</v>
       </c>
       <c r="D96" s="2">
-        <f t="shared" si="2"/>
         <v>351</v>
       </c>
+      <c r="E96">
+        <v>270.92</v>
+      </c>
+      <c r="F96" s="5">
+        <v>307.8</v>
+      </c>
+      <c r="G96" s="2">
+        <f t="shared" si="4"/>
+        <v>80.079999999999984</v>
+      </c>
+      <c r="H96" s="4">
+        <f t="shared" si="5"/>
+        <v>36.879999999999995</v>
+      </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
         <v>19</v>
       </c>
@@ -13122,11 +17048,24 @@
         <v>7.76826843</v>
       </c>
       <c r="D97" s="2">
-        <f t="shared" si="2"/>
         <v>206</v>
       </c>
+      <c r="E97">
+        <v>167.42</v>
+      </c>
+      <c r="F97" s="5">
+        <v>187.85</v>
+      </c>
+      <c r="G97" s="2">
+        <f t="shared" si="4"/>
+        <v>38.580000000000013</v>
+      </c>
+      <c r="H97" s="4">
+        <f t="shared" si="5"/>
+        <v>20.430000000000007</v>
+      </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>27</v>
       </c>
@@ -13138,11 +17077,24 @@
         <v>66.19802722</v>
       </c>
       <c r="D98" s="2">
-        <f t="shared" si="2"/>
         <v>186.9</v>
       </c>
+      <c r="E98">
+        <v>195.12</v>
+      </c>
+      <c r="F98" s="7">
+        <v>208.06</v>
+      </c>
+      <c r="G98" s="2">
+        <f t="shared" si="4"/>
+        <v>-8.2199999999999989</v>
+      </c>
+      <c r="H98" s="4">
+        <f t="shared" si="5"/>
+        <v>12.939999999999998</v>
+      </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
         <v>6</v>
       </c>
@@ -13151,11 +17103,24 @@
         <v>13.486557269999999</v>
       </c>
       <c r="D99" s="2">
-        <f t="shared" si="2"/>
         <v>198</v>
       </c>
+      <c r="E99">
+        <v>263.81</v>
+      </c>
+      <c r="F99" s="5">
+        <v>223.67</v>
+      </c>
+      <c r="G99" s="2">
+        <f t="shared" si="4"/>
+        <v>-65.81</v>
+      </c>
+      <c r="H99" s="4">
+        <f t="shared" si="5"/>
+        <v>-40.140000000000015</v>
+      </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
         <v>7</v>
       </c>
@@ -13164,11 +17129,24 @@
         <v>14.58223203</v>
       </c>
       <c r="D100" s="2">
-        <f t="shared" si="2"/>
         <v>337</v>
       </c>
+      <c r="E100">
+        <v>378.26</v>
+      </c>
+      <c r="F100" s="5">
+        <v>345.61</v>
+      </c>
+      <c r="G100" s="2">
+        <f t="shared" si="4"/>
+        <v>-41.259999999999991</v>
+      </c>
+      <c r="H100" s="4">
+        <f t="shared" si="5"/>
+        <v>-32.649999999999977</v>
+      </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
         <v>8</v>
       </c>
@@ -13177,11 +17155,24 @@
         <v>61.985700940000001</v>
       </c>
       <c r="D101" s="2">
-        <f t="shared" si="2"/>
         <v>189.6</v>
       </c>
+      <c r="E101">
+        <v>226.95</v>
+      </c>
+      <c r="F101" s="5">
+        <v>223.14</v>
+      </c>
+      <c r="G101" s="2">
+        <f t="shared" si="4"/>
+        <v>-37.349999999999994</v>
+      </c>
+      <c r="H101" s="4">
+        <f t="shared" si="5"/>
+        <v>-3.8100000000000023</v>
+      </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>29</v>
       </c>
@@ -13193,11 +17184,24 @@
         <v>38.822217160000001</v>
       </c>
       <c r="D102" s="2">
-        <f t="shared" si="2"/>
         <v>263</v>
       </c>
+      <c r="E102">
+        <v>261.54000000000002</v>
+      </c>
+      <c r="F102" s="5">
+        <v>274.22000000000003</v>
+      </c>
+      <c r="G102" s="2">
+        <f t="shared" si="4"/>
+        <v>1.4599999999999795</v>
+      </c>
+      <c r="H102" s="4">
+        <f t="shared" si="5"/>
+        <v>12.680000000000007</v>
+      </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
         <v>10</v>
       </c>
@@ -13206,11 +17210,24 @@
         <v>40.82876701</v>
       </c>
       <c r="D103" s="2">
-        <f t="shared" si="2"/>
         <v>161.5</v>
       </c>
+      <c r="E103">
+        <v>205.73</v>
+      </c>
+      <c r="F103" s="5">
+        <v>170.05</v>
+      </c>
+      <c r="G103" s="2">
+        <f t="shared" si="4"/>
+        <v>-44.22999999999999</v>
+      </c>
+      <c r="H103" s="4">
+        <f t="shared" si="5"/>
+        <v>-35.679999999999978</v>
+      </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>11</v>
       </c>
@@ -13219,12 +17236,53 @@
         <v>7.1747951170000004</v>
       </c>
       <c r="D104" s="2">
-        <f t="shared" si="2"/>
         <v>166.5</v>
       </c>
+      <c r="E104">
+        <v>209.25</v>
+      </c>
+      <c r="F104" s="5">
+        <v>201.57</v>
+      </c>
+      <c r="G104" s="2">
+        <f t="shared" si="4"/>
+        <v>-42.75</v>
+      </c>
+      <c r="H104" s="4">
+        <f t="shared" si="5"/>
+        <v>-7.6800000000000068</v>
+      </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="D105" s="2"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D106" s="4">
+        <f>AVERAGE(D94:D104)</f>
+        <v>251.5</v>
+      </c>
+      <c r="E106" s="4">
+        <f>AVERAGE(E94:E104)</f>
+        <v>252.95363636363638</v>
+      </c>
+      <c r="F106" s="4">
+        <f>AVERAGE(F94:F104)</f>
+        <v>259.02454545454543</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D107" s="4">
+        <f>_xlfn.STDEV.P(D94:D104)/SQRT(COUNT(D94:D104))</f>
+        <v>23.447765052354431</v>
+      </c>
+      <c r="E107" s="4">
+        <f>_xlfn.STDEV.P(E94:E104)/SQRT(COUNT(E94:E104))</f>
+        <v>17.523952169083955</v>
+      </c>
+      <c r="F107" s="4">
+        <f>_xlfn.STDEV.P(F94:F104)/SQRT(COUNT(F94:F104))</f>
+        <v>20.345138894441369</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A45:G45" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -13239,6 +17297,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Results/Summary.xlsx
+++ b/Results/Summary.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://biu365-my.sharepoint.com/personal/samoily_biu_ac_il/Documents/Academic/Postdoc/Multiplexed analyses/IMC/Results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="260" documentId="11_F25DC773A252ABDACC1048A339584C225BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76B7E37F-F0F2-4F43-BA78-0195C7DCEC3F}"/>
+  <xr:revisionPtr revIDLastSave="306" documentId="11_F25DC773A252ABDACC1048A339584C225BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAD83873-CFA4-4F36-BF6E-3AA61EA55298}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$45:$G$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$45:$J$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Dataset</t>
   </si>
@@ -135,22 +136,118 @@
     <t>C45</t>
   </si>
   <si>
-    <t>J2D + PCA</t>
-  </si>
-  <si>
     <t>avg corr</t>
   </si>
   <si>
     <t>ΔPCA</t>
   </si>
   <si>
-    <t>J2D - no PCA</t>
-  </si>
-  <si>
     <t>ΔPCA + Frozen conv1</t>
   </si>
   <si>
-    <t>J2D + PCA + Frozen conv1</t>
+    <t>HyperConv</t>
+  </si>
+  <si>
+    <t>Per marker</t>
+  </si>
+  <si>
+    <t>Joint</t>
+  </si>
+  <si>
+    <t>Avg.</t>
+  </si>
+  <si>
+    <t>Joint Res-UNet</t>
+  </si>
+  <si>
+    <t>ResUNet (PCA)</t>
+  </si>
+  <si>
+    <t>Res-UNet</t>
+  </si>
+  <si>
+    <t>Res-UNet (PCA-&gt; conv1)</t>
+  </si>
+  <si>
+    <t>HyperConv + aug.</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>ki_67</t>
+  </si>
+  <si>
+    <t>cd20</t>
+  </si>
+  <si>
+    <t>cd3</t>
+  </si>
+  <si>
+    <t>cd45</t>
+  </si>
+  <si>
+    <t>cd68</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Correlation</t>
+  </si>
+  <si>
+    <t>For each target marker, the remaining 10 shared non-control markers are used as inputs. Each input channel is preprocessed by fitting an SGDRegressor that predicts it from the 3 structural controls (Histone H3, DNA1, DNA2), then computing the arcsinh-transformed residual. These 10 residual channels are then jointly compressed to 3 PCA components (fitted on the training set) and z-scored in that 3D space. The 3-channel image is passed to a ResNet50-UNet with a randomly initialised first conv layer. A separate model is trained independently for each of the 11 target markers — 11 training runs total, each on Jackson2020, evaluated on Danenberg2022.</t>
+  </si>
+  <si>
+    <t>Same regression residual preprocessing as the baseline — SGDRegressor per input channel, arcsinh of residuals — but the PCA compression is dropped. Each of the 10 residual channels is z-scored individually using training-set statistics, and all 10 are passed directly to a ResNet50-UNet with a 10-channel first conv layer. A single model is trained jointly on all 11 marker-prediction tasks: each training sample is an (image, target-marker) pair, and the model has no access to marker identity — it must infer what to predict from the input channel ordering alone.</t>
+  </si>
+  <si>
+    <t>Identical input preprocessing to no_pca: same regression residuals, same arcsinh, same per-channel z-score, same 10 input channels. The only change is in the first layer: the fixed conv1 is replaced by a MarkerStem, a small hypernetwork that receives the vocabulary indices of the 10 input markers, looks up a learned embedding per marker, and projects each embedding into a 7×7 convolutional kernel. The 10 per-marker kernels are applied separately and summed, producing the same 64-channel feature map as the standard stem with matched parameter count. The rest of the architecture and joint training setup is identical to no_pca, but now the model knows which markers it is processing at each batch.</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>SEM</t>
+  </si>
+  <si>
+    <t>ResNet50-UNet</t>
+  </si>
+  <si>
+    <t>Per-marker model + PCA</t>
+  </si>
+  <si>
+    <t>Joint model</t>
+  </si>
+  <si>
+    <t>Joint model + HyperConv.</t>
+  </si>
+  <si>
+    <t>KRTs</t>
+  </si>
+  <si>
+    <t>KRT5</t>
+  </si>
+  <si>
+    <t>KRT8-18</t>
+  </si>
+  <si>
+    <t>Pan-KRT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joint </t>
+  </si>
+  <si>
+    <t>Joint + HyperConv.</t>
+  </si>
+  <si>
+    <t>Per-marker + PCA</t>
+  </si>
+  <si>
+    <t>Markers</t>
+  </si>
+  <si>
+    <t>Str.</t>
   </si>
 </sst>
 </file>
@@ -161,13 +258,26 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -178,7 +288,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -186,11 +296,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -199,6 +320,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -253,6 +380,734 @@
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12486052555281281"/>
+          <c:y val="5.0925925925925923E-2"/>
+          <c:w val="0.86004763888472158"/>
+          <c:h val="0.56019694332705838"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Per-marker + PCA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$A$20:$B$31</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="12"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>ki_67</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Pan-KRT</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>KRT5</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>KRT8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>cd45</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>cd20</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>cd3</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>cd68</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Markers</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>KRTs</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Str.</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Mean</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$20:$C$31</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.57799999999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.17499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.57399999999999995</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.36799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.218</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.14699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.28981818181818181</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8B54-4ABE-811E-127B1A05A0AC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Joint </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$A$20:$B$31</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="12"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>ki_67</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Pan-KRT</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>KRT5</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>KRT8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>cd45</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>cd20</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>cd3</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>cd68</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Markers</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>KRTs</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Str.</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Mean</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$D$20:$D$31</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.58599999999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.41499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.111</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.13500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.39400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.38600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.188</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.23899999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8B54-4ABE-811E-127B1A05A0AC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$E$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Joint + HyperConv.</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$A$20:$B$31</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="12"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>ki_67</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Pan-KRT</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>KRT5</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>KRT8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>cd45</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>cd20</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>cd3</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>cd68</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Markers</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>KRTs</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Str.</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Mean</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$E$20:$E$31</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.63600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.41199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.183</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.38900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.124</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.253</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.39100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.437</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.253</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.157</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.11899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.30490909090909091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8B54-4ABE-811E-127B1A05A0AC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="953149647"/>
+        <c:axId val="953150479"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="953149647"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="953150479"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="953150479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Corr.</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="LID4096"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="953149647"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="0.25"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.78117907648728124"/>
+          <c:y val="3.2985564304461944E-2"/>
+          <c:w val="0.20496904500264984"/>
+          <c:h val="0.22630521042179083"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="LID4096"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1400"/>
+      </a:pPr>
+      <a:endParaRPr lang="LID4096"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="bar"/>
@@ -274,7 +1129,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent2"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -284,32 +1139,35 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$2:$B$7</c:f>
+              <c:f>Sheet1!$A$9:$B$15</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:lvl>
                   <c:pt idx="0">
+                    <c:v>CK8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
                     <c:v>Ki67</c:v>
                   </c:pt>
-                  <c:pt idx="1">
+                  <c:pt idx="2">
+                    <c:v>CK5</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>pHH3</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
                     <c:v>HER2</c:v>
                   </c:pt>
-                  <c:pt idx="2">
-                    <c:v>CK8-18</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>CK5</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
+                  <c:pt idx="5">
                     <c:v>Pan-CK</c:v>
                   </c:pt>
-                  <c:pt idx="5">
-                    <c:v>ERa</c:v>
+                  <c:pt idx="6">
+                    <c:v>H3K27me</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Danenberg</c:v>
+                    <c:v>Jackson</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -317,34 +1175,37 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$7</c:f>
+              <c:f>Sheet1!$E$9:$E$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>340.8</c:v>
+                  <c:v>257.05</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>292.7</c:v>
+                  <c:v>295.01</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>314</c:v>
+                  <c:v>270.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>371.6</c:v>
+                  <c:v>317.12</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>346.6</c:v>
+                  <c:v>240.74</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>257.7</c:v>
+                  <c:v>298.39999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>253.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000010-0B62-49EF-994B-DCDC43AD39EA}"/>
+              <c16:uniqueId val="{00000000-7EF8-448E-8424-F828939EB658}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -530,7 +1391,1032 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.19066409412523769"/>
+          <c:y val="4.6013982938524219E-2"/>
+          <c:w val="0.8092420285807217"/>
+          <c:h val="0.78549247428532487"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$I$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HyperConv + aug.</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$I$78:$I$88</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.19059999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13650000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.29160000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.4743</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.121</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.28460000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.1958</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.45140000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.63780000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8288-436F-8A40-719492950D50}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$H$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HyperConv</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$A$94:$B$104</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="11"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>CD3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>CD68</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>CD20</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>CD45</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Pan-CK</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>CK5</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>CK8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Ki67</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Identity</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$78:$H$88</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.1565</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.11940000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.25340000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.43669999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.39100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.38890000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.12429999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.25259999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.18329999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.41199999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.63560000000000005</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FCCA-4080-9617-B6D2625EA2A0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Res-UNet (PCA-&gt; conv1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$A$94:$B$104</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="11"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>CD3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>CD68</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>CD20</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>CD45</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Pan-CK</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>CK5</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>CK8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Ki67</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Identity</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$78:$F$88</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.13469999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.5600000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.22020000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.38390000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.58699999999999997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.38540000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.1497</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.45429999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.55469999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-51E3-44FD-9875-BE5693CA14EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Res-UNet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$A$94:$B$104</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="11"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>CD3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>CD68</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>CD20</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>CD45</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Pan-CK</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>CK5</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>CK8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Ki67</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Identity</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$78:$E$88</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.188</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.38600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.13500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.39400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.111</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.41499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.58599999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8B98-48E2-A025-73C7EDC32719}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="450038527"/>
+        <c:axId val="450038943"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$G$77</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Joint Res-UNet</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent6"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$94:$B$104</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="11"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>CD3</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>CD68</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>CD20</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>CD45</c:v>
+                        </c:pt>
+                        <c:pt idx="4">
+                          <c:v>sma</c:v>
+                        </c:pt>
+                        <c:pt idx="5">
+                          <c:v>Pan-CK</c:v>
+                        </c:pt>
+                        <c:pt idx="6">
+                          <c:v>CK5</c:v>
+                        </c:pt>
+                        <c:pt idx="7">
+                          <c:v>CK8-18</c:v>
+                        </c:pt>
+                        <c:pt idx="8">
+                          <c:v>Ki67</c:v>
+                        </c:pt>
+                        <c:pt idx="9">
+                          <c:v>HER2</c:v>
+                        </c:pt>
+                        <c:pt idx="10">
+                          <c:v>ERa</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>Immune</c:v>
+                        </c:pt>
+                        <c:pt idx="4">
+                          <c:v>Identity</c:v>
+                        </c:pt>
+                        <c:pt idx="8">
+                          <c:v>Clinical</c:v>
+                        </c:pt>
+                      </c:lvl>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$G$78:$G$88</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="11"/>
+                      <c:pt idx="0">
+                        <c:v>0.1472</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>7.8799999999999995E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.2397</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>0.39240000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>0.37530000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>0.38500000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>0.1037</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>0.26869999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>0.1832</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>0.316</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>0.60829999999999995</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-CAF0-47CA-B540-E68CD22BD110}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="4"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$D$77</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>ResUNet (PCA)</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$94:$B$104</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="11"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>CD3</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>CD68</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>CD20</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>CD45</c:v>
+                        </c:pt>
+                        <c:pt idx="4">
+                          <c:v>sma</c:v>
+                        </c:pt>
+                        <c:pt idx="5">
+                          <c:v>Pan-CK</c:v>
+                        </c:pt>
+                        <c:pt idx="6">
+                          <c:v>CK5</c:v>
+                        </c:pt>
+                        <c:pt idx="7">
+                          <c:v>CK8-18</c:v>
+                        </c:pt>
+                        <c:pt idx="8">
+                          <c:v>Ki67</c:v>
+                        </c:pt>
+                        <c:pt idx="9">
+                          <c:v>HER2</c:v>
+                        </c:pt>
+                        <c:pt idx="10">
+                          <c:v>ERa</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>Immune</c:v>
+                        </c:pt>
+                        <c:pt idx="4">
+                          <c:v>Identity</c:v>
+                        </c:pt>
+                        <c:pt idx="8">
+                          <c:v>Clinical</c:v>
+                        </c:pt>
+                      </c:lvl>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$D$78:$D$88</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="11"/>
+                      <c:pt idx="0">
+                        <c:v>0.14710000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>9.6000000000000002E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.21759999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>0.37040000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>0.13</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>0.57399999999999995</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>8.0799999999999997E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>0.36820000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>0.17499999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>0.45</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>0.57750000000000001</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-EE61-4435-AE78-9073A36085FA}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="450038527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="450038943"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="450038943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="2400"/>
+                  <a:t>Pearson's corr.</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="LID4096"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="450038527"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="0.2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.65121068680031891"/>
+          <c:y val="0.33712374072275819"/>
+          <c:w val="0.27043277862487658"/>
+          <c:h val="0.47171801855981321"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="LID4096"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1600"/>
+      </a:pPr>
+      <a:endParaRPr lang="LID4096"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -562,166 +2448,25 @@
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="3"/>
+          <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$F$77</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>J2D + PCA + Frozen conv1</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="92D050"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$F$94:$F$104</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>335.6</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>371.7</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>307.8</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>187.85</c:v>
-                </c:pt>
-                <c:pt idx="4" formatCode="0.00">
-                  <c:v>208.06</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>223.67</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>345.61</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>223.14</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>274.22000000000003</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>170.05</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>201.57</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-616A-4D55-AD9F-871EEED13386}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="1"/>
           <c:tx>
             <c:strRef>
               <c:f>Sheet1!$E$77</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>J2D - no PCA</c:v>
+                  <c:v>Res-UNet</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$E$94:$E$104</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>320.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>282.99</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>270.92</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>167.42</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>195.12</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>263.81</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>378.26</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>226.95</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>261.54000000000002</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>205.73</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>209.25</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E6B0-4838-A5E9-4E786294BD7E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$77</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>J2D + PCA</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -785,6 +2530,135 @@
           </c:cat>
           <c:val>
             <c:numRef>
+              <c:f>Sheet1!$E$94:$E$104</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>320.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>282.99</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>270.92</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>167.42</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>195.12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>263.81</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>378.26</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>226.95</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>261.54000000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>205.73</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>209.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E6B0-4838-A5E9-4E786294BD7E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ResUNet (PCA)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$A$94:$B$104</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="11"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>CD3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>CD68</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>CD20</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>CD45</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Pan-CK</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>CK5</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>CK8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Ki67</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Identity</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
               <c:f>Sheet1!$D$94:$D$104</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
@@ -828,6 +2702,388 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-3A0D-4632-9F6D-E582F1EAE94B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Res-UNet (PCA-&gt; conv1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$A$94:$B$104</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="11"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>CD3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>CD68</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>CD20</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>CD45</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Pan-CK</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>CK5</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>CK8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Ki67</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Identity</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$94:$F$104</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>335.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>371.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>307.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>187.85</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.00">
+                  <c:v>208.06</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>223.67</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>345.61</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>223.14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>274.22000000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>170.05</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>201.57</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-616A-4D55-AD9F-871EEED13386}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Joint Res-UNet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$A$94:$B$104</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="11"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>CD3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>CD68</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>CD20</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>CD45</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Pan-CK</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>CK5</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>CK8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Ki67</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Identity</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$94:$G$104</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>190.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>182.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>189.68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>239.58</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.00">
+                  <c:v>241.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>260.10000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>218.71</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>200.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>167.77</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>224.26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>317.08</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5927-4B9D-B97F-49E39068292C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$H$77</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HyperConv</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$A$94:$B$104</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="11"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>CD3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>CD68</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>CD20</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>CD45</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Pan-CK</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>CK5</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>CK8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Ki67</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Identity</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$94:$H$104</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>203.67</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>225.73</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>204.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>248.8</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.00">
+                  <c:v>234.77</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>287.91000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>240.87</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>201.04</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>177.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>225.75</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>324.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6015-48EA-A419-28104F845716}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -907,7 +3163,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -920,7 +3176,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
+                  <a:rPr lang="en-US" sz="2400"/>
                   <a:t>FID (lower is better)</a:t>
                 </a:r>
               </a:p>
@@ -939,7 +3195,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -1034,7 +3290,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1549,7 +3805,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1585,7 +3841,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$H$77</c:f>
+              <c:f>Sheet1!$K$77</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1647,7 +3903,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$78:$H$88</c:f>
+              <c:f>Sheet1!$K$78:$K$88</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
@@ -1698,7 +3954,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$G$77</c:f>
+              <c:f>Sheet1!$J$77</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1760,7 +4016,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$78:$G$88</c:f>
+              <c:f>Sheet1!$J$78:$J$88</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
@@ -2053,7 +4309,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2089,7 +4345,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$H$77</c:f>
+              <c:f>Sheet1!$K$77</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2151,7 +4407,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$94:$H$104</c:f>
+              <c:f>Sheet1!$K$94:$K$104</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
@@ -2202,7 +4458,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$G$77</c:f>
+              <c:f>Sheet1!$J$77</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2264,7 +4520,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$94:$G$104</c:f>
+              <c:f>Sheet1!$J$94:$J$104</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="11"/>
@@ -2515,7 +4771,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2761,7 +5017,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>J2D - no PCA</c:v>
+                        <c:v>Res-UNet</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2849,7 +5105,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>J2D + PCA</c:v>
+                        <c:v>ResUNet (PCA)</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2995,7 +5251,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>J2D + PCA + Frozen conv1</c:v>
+                        <c:v>Res-UNet (PCA-&gt; conv1)</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -3279,6 +5535,1029 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
+          <c:x val="0.12486052555281281"/>
+          <c:y val="5.0925925925925923E-2"/>
+          <c:w val="0.86004763888472158"/>
+          <c:h val="0.56210094256341836"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Per-marker + PCA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$A$3:$B$14</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="12"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>ki_67</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Pan-KRT</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>KRT5</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>KRT8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>cd45</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>cd20</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>cd3</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>cd68</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Markers</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>KRTs</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Str.</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Mean</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$3:$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>166.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>161.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>263.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>198.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>337.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>189.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>186.9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>206.2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>351.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>346.3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>361.3</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.0">
+                  <c:v>251.73636363636368</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3136-4067-859E-5C71F059A01F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Joint </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$A$3:$B$14</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="12"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>ki_67</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Pan-KRT</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>KRT5</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>KRT8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>cd45</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>cd20</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>cd3</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>cd68</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Markers</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>KRTs</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Str.</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Mean</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$D$3:$D$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>209.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>205.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>261.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>263.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>378.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>227</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>195.1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>167.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>270.89999999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>320.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>282.89999999999998</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.0">
+                  <c:v>252.93636363636367</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3136-4067-859E-5C71F059A01F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$E$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Joint + HyperConv.</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$A$3:$B$14</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="12"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>ki_67</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Pan-KRT</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>KRT5</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>KRT8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>sma</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>cd45</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>cd20</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>cd3</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>cd68</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Markers</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Clinical</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>KRTs</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Str.</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Immune</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Mean</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$E$3:$E$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>324.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>225.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>177.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>287.89999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>240.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>234.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>248.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>204.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>203.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>225.7</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.0">
+                  <c:v>234.06363636363633</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3136-4067-859E-5C71F059A01F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="953149647"/>
+        <c:axId val="953150479"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="953149647"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="953150479"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="953150479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="500"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>FID</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="LID4096"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="953149647"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="250"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.48223007270491491"/>
+          <c:y val="7.0001664997418708E-2"/>
+          <c:w val="0.20496904500264984"/>
+          <c:h val="0.19391609214540201"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="LID4096"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1400"/>
+      </a:pPr>
+      <a:endParaRPr lang="LID4096"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>FID</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$A$2:$B$7</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="6"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Ki67</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>HER2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>CK8-18</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>CK5</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Pan-CK</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>ERa</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Danenberg</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>340.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>292.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>314</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>371.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>346.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>257.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000010-0B62-49EF-994B-DCDC43AD39EA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="457638511"/>
+        <c:axId val="457638927"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="457638511"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="457638927"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="457638927"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>FID</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="LID4096"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="457638511"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="100"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1400"/>
+      </a:pPr>
+      <a:endParaRPr lang="LID4096"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
           <c:x val="0.12447286784294566"/>
           <c:y val="4.8198723648115505E-2"/>
           <c:w val="0.83207577146879064"/>
@@ -3698,7 +6977,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4328,7 +7607,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4900,7 +8179,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5284,7 +8563,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5756,7 +9035,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6228,956 +9507,6 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="1400"/>
-      </a:pPr>
-      <a:endParaRPr lang="LID4096"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>FID</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$9:$B$15</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="7"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>CK8-18</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Ki67</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>CK5</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>pHH3</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>HER2</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Pan-CK</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>H3K27me</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Jackson</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$E$9:$E$15</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>257.05</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>295.01</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>270.7</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>317.12</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>240.74</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>298.39999999999998</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>253.4</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7EF8-448E-8424-F828939EB658}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="457638511"/>
-        <c:axId val="457638927"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="457638511"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="457638927"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="457638927"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>FID</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="LID4096"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="LID4096"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="457638511"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="100"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:noFill/>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr sz="1400"/>
-      </a:pPr>
-      <a:endParaRPr lang="LID4096"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.19226655399373865"/>
-          <c:y val="1.8394128161786191E-2"/>
-          <c:w val="0.8092420285807217"/>
-          <c:h val="0.82350501489426831"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$77</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>J2D - no PCA</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$94:$B$104</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="11"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>CD3</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>CD68</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>CD20</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>CD45</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>sma</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Pan-CK</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>CK5</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>CK8-18</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>Ki67</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>HER2</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>ERa</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Immune</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Identity</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>Clinical</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$E$78:$E$88</c:f>
-              <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.16</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.188</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.38600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.5999999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.13500000000000001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7.8E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.39400000000000002</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.111</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.41499999999999998</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.58599999999999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8B98-48E2-A025-73C7EDC32719}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$F$77</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>J2D + PCA + Frozen conv1</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="92D050"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$94:$B$104</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="11"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>CD3</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>CD68</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>CD20</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>CD45</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>sma</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Pan-CK</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>CK5</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>CK8-18</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>Ki67</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>HER2</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>ERa</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Immune</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Identity</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>Clinical</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$F$78:$F$88</c:f>
-              <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>0.13469999999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9.5600000000000004E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.22020000000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.38390000000000002</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6.2E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.58699999999999997</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7.5999999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.38540000000000002</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.1497</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.45429999999999998</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.55469999999999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-51E3-44FD-9875-BE5693CA14EC}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$D$77</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>J2D + PCA</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>Sheet1!$A$94:$B$104</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="11"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>CD3</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>CD68</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>CD20</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>CD45</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>sma</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>Pan-CK</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>CK5</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>CK8-18</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>Ki67</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>HER2</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>ERa</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Immune</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Identity</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>Clinical</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$D$78:$D$88</c:f>
-              <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>0.14710000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9.6000000000000002E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.21759999999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.37040000000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.57399999999999995</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>8.0799999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.36820000000000003</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.17499999999999999</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.45</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.57750000000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EE61-4435-AE78-9073A36085FA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="450038527"/>
-        <c:axId val="450038943"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="450038527"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="LID4096"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="450038943"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="450038943"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="1"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Pearson's corr.</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="LID4096"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="LID4096"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="450038527"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="0.2"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.58113639061461198"/>
-          <c:y val="0.49740609742409458"/>
-          <c:w val="0.40051121570329662"/>
-          <c:h val="0.32701807882257833"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="LID4096"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:noFill/>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr sz="1600"/>
       </a:pPr>
       <a:endParaRPr lang="LID4096"/>
     </a:p>
@@ -7391,6 +9720,86 @@
 </file>
 
 <file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors16.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -7751,7 +10160,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -7955,23 +10364,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -8076,8 +10484,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8209,20 +10617,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -10780,7 +13187,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -11285,7 +13692,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -11790,8 +14197,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -11995,23 +14402,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -12116,8 +14522,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -12249,20 +14655,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -12295,7 +14700,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -12800,7 +15205,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -13305,7 +15710,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -13810,7 +16215,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -14315,7 +16720,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -14820,17 +17225,1108 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>251810</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>136854</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>207983</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>89792</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F1C60B1-C0E5-40DA-8A18-49BF37C07010}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>563803</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>139059</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1613F45-4645-4CC4-9053-C6BE2590F64F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>272030</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>45356</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>349249</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>31749</xdr:rowOff>
@@ -14862,13 +18358,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>118783</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>118393</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>403599</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>120837</xdr:rowOff>
@@ -14898,13 +18394,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>453515</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>117245</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>43</xdr:col>
+      <xdr:col>46</xdr:col>
       <xdr:colOff>500742</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>38904</xdr:rowOff>
@@ -14942,7 +18438,7 @@
       <xdr:rowOff>76759</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>286747</xdr:colOff>
       <xdr:row>149</xdr:row>
       <xdr:rowOff>58942</xdr:rowOff>
@@ -14974,13 +18470,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>18900</xdr:colOff>
       <xdr:row>130</xdr:row>
       <xdr:rowOff>30298</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>112297</xdr:colOff>
       <xdr:row>149</xdr:row>
       <xdr:rowOff>25378</xdr:rowOff>
@@ -15012,13 +18508,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>22412</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>53663</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>592502</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>108091</xdr:rowOff>
@@ -15050,13 +18546,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>570090</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>54428</xdr:rowOff>
@@ -15088,13 +18584,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>77219</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>176893</xdr:rowOff>
@@ -15126,16 +18622,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>543350</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>153279</xdr:colOff>
       <xdr:row>75</xdr:row>
       <xdr:rowOff>46837</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>305287</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>12309</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>523002</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15164,16 +18660,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>39933</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>8295</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>121576</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>53653</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>354133</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>653</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>11545</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>23091</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15202,13 +18698,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>138398</xdr:colOff>
       <xdr:row>151</xdr:row>
       <xdr:rowOff>103065</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>540951</xdr:colOff>
       <xdr:row>170</xdr:row>
       <xdr:rowOff>104495</xdr:rowOff>
@@ -15240,13 +18736,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>120478</xdr:colOff>
       <xdr:row>74</xdr:row>
       <xdr:rowOff>152401</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>214630</xdr:colOff>
       <xdr:row>97</xdr:row>
       <xdr:rowOff>117874</xdr:rowOff>
@@ -15278,13 +18774,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>192129</xdr:colOff>
       <xdr:row>98</xdr:row>
       <xdr:rowOff>84831</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>293006</xdr:colOff>
       <xdr:row>121</xdr:row>
       <xdr:rowOff>83539</xdr:rowOff>
@@ -15316,16 +18812,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>344714</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:rowOff>16329</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>100878</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>445591</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>17758</xdr:rowOff>
+      <xdr:rowOff>8687</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15355,7 +18851,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
@@ -15411,7 +18907,7 @@
 </c:userShapes>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
@@ -15729,19 +19225,507 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H107"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CB3BE29-5887-47D2-B6DB-21DD0F45101E}">
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>166.5</v>
+      </c>
+      <c r="D3">
+        <v>209.2</v>
+      </c>
+      <c r="E3">
+        <v>324.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>161.5</v>
+      </c>
+      <c r="D4">
+        <v>205.7</v>
+      </c>
+      <c r="E4">
+        <v>225.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5">
+        <v>263.2</v>
+      </c>
+      <c r="D5">
+        <v>261.5</v>
+      </c>
+      <c r="E5">
+        <v>177.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6">
+        <v>198.5</v>
+      </c>
+      <c r="D6">
+        <v>263.8</v>
+      </c>
+      <c r="E6">
+        <v>287.89999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>337.9</v>
+      </c>
+      <c r="D7">
+        <v>378.3</v>
+      </c>
+      <c r="E7">
+        <v>240.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8">
+        <v>189.6</v>
+      </c>
+      <c r="D8">
+        <v>227</v>
+      </c>
+      <c r="E8">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9">
+        <v>186.9</v>
+      </c>
+      <c r="D9">
+        <v>195.1</v>
+      </c>
+      <c r="E9">
+        <v>234.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10">
+        <v>206.2</v>
+      </c>
+      <c r="D10">
+        <v>167.4</v>
+      </c>
+      <c r="E10">
+        <v>248.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11">
+        <v>351.2</v>
+      </c>
+      <c r="D11">
+        <v>270.89999999999998</v>
+      </c>
+      <c r="E11">
+        <v>204.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12">
+        <v>346.3</v>
+      </c>
+      <c r="D12">
+        <v>320.5</v>
+      </c>
+      <c r="E12">
+        <v>203.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13">
+        <v>361.3</v>
+      </c>
+      <c r="D13">
+        <v>282.89999999999998</v>
+      </c>
+      <c r="E13">
+        <v>225.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="9">
+        <f>AVERAGE(C1:C13)</f>
+        <v>251.73636363636368</v>
+      </c>
+      <c r="D14" s="9">
+        <f>AVERAGE(D1:D13)</f>
+        <v>252.93636363636367</v>
+      </c>
+      <c r="E14" s="9">
+        <f>AVERAGE(E1:E13)</f>
+        <v>234.06363636363633</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B15" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="2">
+        <f>_xlfn.STDEV.S(C3:C13)/SQRT(COUNT(C3:C13))</f>
+        <v>24.638341416755154</v>
+      </c>
+      <c r="D15" s="2">
+        <f>_xlfn.STDEV.S(D3:D13)/SQRT(COUNT(D3:D13))</f>
+        <v>18.382577090709233</v>
+      </c>
+      <c r="E15" s="2">
+        <f>_xlfn.STDEV.S(E3:E13)/SQRT(COUNT(E3:E13))</f>
+        <v>12.646675975256962</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0.63600000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0.45</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0.41199999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="4">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0.111</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0.183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="4">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0.38900000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="4">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="D24" s="4">
+        <v>7.8E-2</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="4">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0.253</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="4">
+        <v>0.13</v>
+      </c>
+      <c r="D26" s="4">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="E26" s="4">
+        <v>0.39100000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="4">
+        <v>0.37</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0.437</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="4">
+        <v>0.218</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0.188</v>
+      </c>
+      <c r="E28" s="4">
+        <v>0.253</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="4">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0.157</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="4">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.16</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0.11899999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="10">
+        <f>AVERAGE(C20:C30)</f>
+        <v>0.28981818181818181</v>
+      </c>
+      <c r="D31" s="10">
+        <f>AVERAGE(D20:D30)</f>
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="E31" s="10">
+        <f>AVERAGE(E20:E30)</f>
+        <v>0.30490909090909091</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="4">
+        <f>_xlfn.STDEV.S(C20:C30)/SQRT(COUNT(C20:C30))</f>
+        <v>5.617113755493007E-2</v>
+      </c>
+      <c r="D32" s="4">
+        <f>_xlfn.STDEV.S(D20:D30)/SQRT(COUNT(D20:D30))</f>
+        <v>5.3280731635708269E-2</v>
+      </c>
+      <c r="E32" s="4">
+        <f>_xlfn.STDEV.S(E20:E30)/SQRT(COUNT(E20:E30))</f>
+        <v>4.884473630252098E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K107"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="7.08984375" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="22.08984375" customWidth="1"/>
+    <col min="10" max="10" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15760,11 +19744,11 @@
       <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -15784,7 +19768,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>10</v>
       </c>
@@ -15801,7 +19785,7 @@
         <v>0.16400000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>8</v>
       </c>
@@ -15818,7 +19802,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -15835,7 +19819,7 @@
         <v>0.111</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>6</v>
       </c>
@@ -15852,7 +19836,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -15869,7 +19853,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>30</v>
       </c>
@@ -15877,7 +19861,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -15896,11 +19880,11 @@
       <c r="F9">
         <v>-0.10199999999999999</v>
       </c>
-      <c r="G9">
+      <c r="J9">
         <v>163</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>9</v>
       </c>
@@ -15916,11 +19900,11 @@
       <c r="F10">
         <v>-0.113</v>
       </c>
-      <c r="G10">
+      <c r="J10">
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>7</v>
       </c>
@@ -15937,7 +19921,7 @@
         <v>-0.115</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>14</v>
       </c>
@@ -15953,11 +19937,11 @@
       <c r="F12">
         <v>-0.13600000000000001</v>
       </c>
-      <c r="G12">
+      <c r="J12">
         <v>160</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>10</v>
       </c>
@@ -15973,11 +19957,11 @@
       <c r="F13">
         <v>-0.155</v>
       </c>
-      <c r="G13">
+      <c r="J13">
         <v>158</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>6</v>
       </c>
@@ -15993,11 +19977,11 @@
       <c r="F14">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="G14">
+      <c r="J14">
         <v>117</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>13</v>
       </c>
@@ -16014,7 +19998,7 @@
         <v>-0.13700000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>19</v>
       </c>
@@ -16022,7 +20006,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C18" t="s">
         <v>24</v>
       </c>
@@ -16036,7 +20020,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>6</v>
       </c>
@@ -16052,7 +20036,7 @@
         <v>0.318</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>7</v>
       </c>
@@ -16068,7 +20052,7 @@
         <v>0.379</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>8</v>
       </c>
@@ -16084,7 +20068,7 @@
         <v>0.40100000000000002</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>9</v>
       </c>
@@ -16100,7 +20084,7 @@
         <v>0.39100000000000001</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>10</v>
       </c>
@@ -16116,7 +20100,7 @@
         <v>0.35099999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D25" t="s">
         <v>5</v>
       </c>
@@ -16124,7 +20108,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>6</v>
       </c>
@@ -16143,8 +20127,11 @@
         <f>C14</f>
         <v>0.20128612370691801</v>
       </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>7</v>
       </c>
@@ -16163,8 +20150,11 @@
         <f>C11</f>
         <v>0.31836085952235299</v>
       </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>8</v>
       </c>
@@ -16183,8 +20173,11 @@
         <f>C9</f>
         <v>0.27749155771600498</v>
       </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>9</v>
       </c>
@@ -16203,8 +20196,11 @@
         <f>C10</f>
         <v>0.25666775391575802</v>
       </c>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>10</v>
       </c>
@@ -16223,8 +20219,11 @@
         <f>C13</f>
         <v>0.43841542505719</v>
       </c>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C32" t="s">
         <v>24</v>
       </c>
@@ -16598,7 +20597,7 @@
         <v>189.6</v>
       </c>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
         <v>19</v>
       </c>
@@ -16610,7 +20609,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>10</v>
       </c>
@@ -16622,7 +20621,7 @@
         <v>161.5</v>
       </c>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
         <v>6</v>
       </c>
@@ -16634,7 +20633,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
         <v>11</v>
       </c>
@@ -16646,27 +20645,49 @@
         <v>166.5</v>
       </c>
     </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="D75" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="D76" t="s">
+        <v>35</v>
+      </c>
+      <c r="G76" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F77" t="s">
+        <v>41</v>
+      </c>
+      <c r="G77" t="s">
+        <v>38</v>
+      </c>
+      <c r="H77" t="s">
         <v>34</v>
       </c>
-      <c r="F77" t="s">
-        <v>36</v>
-      </c>
-      <c r="G77" t="s">
+      <c r="I77" t="s">
+        <v>42</v>
+      </c>
+      <c r="J77" t="s">
+        <v>32</v>
+      </c>
+      <c r="K77" t="s">
         <v>33</v>
       </c>
-      <c r="H77" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>18</v>
       </c>
@@ -16679,16 +20700,25 @@
       <c r="F78" s="6">
         <v>0.13469999999999999</v>
       </c>
-      <c r="G78" s="4">
+      <c r="G78" s="6">
+        <v>0.1472</v>
+      </c>
+      <c r="H78" s="6">
+        <v>0.1565</v>
+      </c>
+      <c r="I78" s="6">
+        <v>0.19059999999999999</v>
+      </c>
+      <c r="J78" s="4">
         <f>D78-E78</f>
         <v>-2.8999999999999859E-3</v>
       </c>
-      <c r="H78" s="4">
+      <c r="K78" s="4">
         <f>IF(F78&lt;&gt;"",F78-E78, 0)</f>
         <v>-1.5300000000000008E-2</v>
       </c>
     </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>20</v>
       </c>
@@ -16701,16 +20731,25 @@
       <c r="F79" s="6">
         <v>9.5600000000000004E-2</v>
       </c>
-      <c r="G79" s="4">
-        <f t="shared" ref="G79:G88" si="1">D79-E79</f>
+      <c r="G79" s="6">
+        <v>7.8799999999999995E-2</v>
+      </c>
+      <c r="H79" s="6">
+        <v>0.11940000000000001</v>
+      </c>
+      <c r="I79" s="6">
+        <v>0.13650000000000001</v>
+      </c>
+      <c r="J79" s="4">
+        <f t="shared" ref="J79:J88" si="1">D79-E79</f>
         <v>-6.4000000000000001E-2</v>
       </c>
-      <c r="H79" s="4">
+      <c r="K79" s="4">
         <f>IF(F79&lt;&gt;"",F79-E79, 0)</f>
         <v>-6.4399999999999999E-2</v>
       </c>
     </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>17</v>
       </c>
@@ -16723,16 +20762,25 @@
       <c r="F80" s="6">
         <v>0.22020000000000001</v>
       </c>
-      <c r="G80" s="4">
+      <c r="G80" s="6">
+        <v>0.2397</v>
+      </c>
+      <c r="H80" s="6">
+        <v>0.25340000000000001</v>
+      </c>
+      <c r="I80" s="6">
+        <v>0.29160000000000003</v>
+      </c>
+      <c r="J80" s="4">
         <f t="shared" si="1"/>
         <v>2.9599999999999987E-2</v>
       </c>
-      <c r="H80" s="4">
-        <f t="shared" ref="H80:H88" si="2">IF(F80&lt;&gt;"",F80-E80, 0)</f>
+      <c r="K80" s="4">
+        <f t="shared" ref="K80:K88" si="2">IF(F80&lt;&gt;"",F80-E80, 0)</f>
         <v>3.2200000000000006E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>19</v>
       </c>
@@ -16745,16 +20793,25 @@
       <c r="F81" s="6">
         <v>0.38390000000000002</v>
       </c>
-      <c r="G81" s="4">
+      <c r="G81" s="6">
+        <v>0.39240000000000003</v>
+      </c>
+      <c r="H81" s="6">
+        <v>0.43669999999999998</v>
+      </c>
+      <c r="I81" s="6">
+        <v>0.4743</v>
+      </c>
+      <c r="J81" s="4">
         <f t="shared" si="1"/>
         <v>-1.5600000000000003E-2</v>
       </c>
-      <c r="H81" s="4">
+      <c r="K81" s="4">
         <f t="shared" si="2"/>
         <v>-2.0999999999999908E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>21</v>
       </c>
@@ -16767,16 +20824,23 @@
       <c r="F82" s="6">
         <v>6.2E-2</v>
       </c>
-      <c r="G82" s="4">
+      <c r="G82" s="6">
+        <v>0.37530000000000002</v>
+      </c>
+      <c r="H82" s="6">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="I82" s="6"/>
+      <c r="J82" s="4">
         <f t="shared" si="1"/>
         <v>0.10400000000000001</v>
       </c>
-      <c r="H82" s="4">
+      <c r="K82" s="4">
         <f t="shared" si="2"/>
         <v>3.6000000000000004E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>6</v>
       </c>
@@ -16789,16 +20853,23 @@
       <c r="F83" s="6">
         <v>0.58699999999999997</v>
       </c>
-      <c r="G83" s="4">
+      <c r="G83" s="6">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="H83" s="6">
+        <v>0.38890000000000002</v>
+      </c>
+      <c r="I83" s="6"/>
+      <c r="J83" s="4">
         <f t="shared" si="1"/>
         <v>0.43899999999999995</v>
       </c>
-      <c r="H83" s="4">
+      <c r="K83" s="4">
         <f t="shared" si="2"/>
         <v>0.45199999999999996</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>7</v>
       </c>
@@ -16811,16 +20882,25 @@
       <c r="F84" s="6">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="G84" s="4">
+      <c r="G84" s="6">
+        <v>0.1037</v>
+      </c>
+      <c r="H84" s="6">
+        <v>0.12429999999999999</v>
+      </c>
+      <c r="I84" s="6">
+        <v>0.121</v>
+      </c>
+      <c r="J84" s="4">
         <f t="shared" si="1"/>
         <v>2.7999999999999969E-3</v>
       </c>
-      <c r="H84" s="4">
+      <c r="K84" s="4">
         <f t="shared" si="2"/>
         <v>-2.0000000000000018E-3</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>8</v>
       </c>
@@ -16833,16 +20913,25 @@
       <c r="F85" s="6">
         <v>0.38540000000000002</v>
       </c>
-      <c r="G85" s="4">
+      <c r="G85" s="6">
+        <v>0.26869999999999999</v>
+      </c>
+      <c r="H85" s="6">
+        <v>0.25259999999999999</v>
+      </c>
+      <c r="I85" s="6">
+        <v>0.28460000000000002</v>
+      </c>
+      <c r="J85" s="4">
         <f t="shared" si="1"/>
         <v>-2.579999999999999E-2</v>
       </c>
-      <c r="H85" s="4">
+      <c r="K85" s="4">
         <f t="shared" si="2"/>
         <v>-8.5999999999999965E-3</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>9</v>
       </c>
@@ -16855,16 +20944,25 @@
       <c r="F86" s="6">
         <v>0.1497</v>
       </c>
-      <c r="G86" s="4">
+      <c r="G86" s="6">
+        <v>0.1832</v>
+      </c>
+      <c r="H86" s="6">
+        <v>0.18329999999999999</v>
+      </c>
+      <c r="I86" s="6">
+        <v>0.1958</v>
+      </c>
+      <c r="J86" s="4">
         <f t="shared" si="1"/>
         <v>6.3999999999999987E-2</v>
       </c>
-      <c r="H86" s="4">
+      <c r="K86" s="4">
         <f t="shared" si="2"/>
         <v>3.8699999999999998E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>10</v>
       </c>
@@ -16877,16 +20975,25 @@
       <c r="F87" s="6">
         <v>0.45429999999999998</v>
       </c>
-      <c r="G87" s="4">
+      <c r="G87" s="6">
+        <v>0.316</v>
+      </c>
+      <c r="H87" s="6">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="I87" s="6">
+        <v>0.45140000000000002</v>
+      </c>
+      <c r="J87" s="4">
         <f t="shared" si="1"/>
         <v>3.5000000000000031E-2</v>
       </c>
-      <c r="H87" s="4">
+      <c r="K87" s="4">
         <f t="shared" si="2"/>
         <v>3.9300000000000002E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>11</v>
       </c>
@@ -16899,66 +21006,102 @@
       <c r="F88" s="6">
         <v>0.55469999999999997</v>
       </c>
-      <c r="G88" s="4">
+      <c r="G88" s="6">
+        <v>0.60829999999999995</v>
+      </c>
+      <c r="H88" s="6">
+        <v>0.63560000000000005</v>
+      </c>
+      <c r="I88" s="6">
+        <v>0.63780000000000003</v>
+      </c>
+      <c r="J88" s="4">
         <f t="shared" si="1"/>
         <v>-8.499999999999952E-3</v>
       </c>
-      <c r="H88" s="4">
+      <c r="K88" s="4">
         <f t="shared" si="2"/>
         <v>-3.1299999999999994E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C90" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D90" s="1">
-        <f>AVERAGE(D77:D88)</f>
+        <f t="shared" ref="D90:K90" si="3">AVERAGE(D77:D88)</f>
         <v>0.28969090909090911</v>
       </c>
       <c r="E90" s="1">
-        <f>AVERAGE(E77:E88)</f>
+        <f t="shared" si="3"/>
         <v>0.23899999999999996</v>
       </c>
       <c r="F90" s="1">
-        <f>AVERAGE(F77:F88)</f>
+        <f t="shared" si="3"/>
         <v>0.28213636363636363</v>
       </c>
       <c r="G90" s="1">
-        <f>AVERAGE(G77:G88)</f>
+        <f t="shared" si="3"/>
+        <v>0.28166363636363634</v>
+      </c>
+      <c r="H90" s="1">
+        <f t="shared" si="3"/>
+        <v>0.3048818181818182</v>
+      </c>
+      <c r="I90" s="1">
+        <f t="shared" si="3"/>
+        <v>0.30928888888888889</v>
+      </c>
+      <c r="J90" s="1">
+        <f t="shared" si="3"/>
         <v>5.0690909090909099E-2</v>
       </c>
-      <c r="H90" s="1">
-        <f>AVERAGE(H77:H88)</f>
+      <c r="K90" s="1">
+        <f>AVERAGE(K77:K88)</f>
         <v>4.3136363636363639E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D91" s="4">
-        <f>_xlfn.STDEV.P(D78:D88)/SQRT(COUNT(D78:D88))</f>
+        <f t="shared" ref="D91:K91" si="4">_xlfn.STDEV.P(D78:D88)/SQRT(COUNT(D78:D88))</f>
         <v>5.3580742276494009E-2</v>
       </c>
       <c r="E91" s="4">
-        <f>_xlfn.STDEV.P(E78:E88)/SQRT(COUNT(E78:E88))</f>
+        <f t="shared" si="4"/>
         <v>5.0801184342281966E-2</v>
       </c>
       <c r="F91" s="4">
-        <f>_xlfn.STDEV.P(F78:F88)/SQRT(COUNT(F78:F88))</f>
+        <f t="shared" si="4"/>
         <v>5.6535904298339081E-2</v>
       </c>
       <c r="G91" s="4">
-        <f>_xlfn.STDEV.P(G78:G88)/SQRT(COUNT(G78:G88))</f>
+        <f t="shared" si="4"/>
+        <v>4.4731363953181079E-2</v>
+      </c>
+      <c r="H91" s="4">
+        <f t="shared" si="4"/>
+        <v>4.6523487035909784E-2</v>
+      </c>
+      <c r="I91" s="4">
+        <f t="shared" si="4"/>
+        <v>5.5393286227864158E-2</v>
+      </c>
+      <c r="J91" s="4">
+        <f t="shared" si="4"/>
         <v>3.9266246213005965E-2</v>
       </c>
-      <c r="H91" s="4">
-        <f>_xlfn.STDEV.P(H78:H88)/SQRT(COUNT(H78:H88))</f>
+      <c r="K91" s="4">
+        <f t="shared" si="4"/>
         <v>4.0108770032358763E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>28</v>
       </c>
@@ -16978,21 +21121,30 @@
       <c r="F94" s="5">
         <v>335.6</v>
       </c>
-      <c r="G94" s="2">
+      <c r="G94" s="5">
+        <v>190.6</v>
+      </c>
+      <c r="H94" s="5">
+        <v>203.67</v>
+      </c>
+      <c r="I94" s="5">
+        <v>207.77</v>
+      </c>
+      <c r="J94" s="2">
         <f>D94-E94</f>
         <v>25.5</v>
       </c>
-      <c r="H94" s="4">
+      <c r="K94" s="4">
         <f>IF(F94&lt;&gt;"",F94-E94, 0)</f>
         <v>15.100000000000023</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>20</v>
       </c>
       <c r="C95" s="3">
-        <f t="shared" ref="C95:C104" si="3">VLOOKUP(B95,$B$58:$D$68,2,0)</f>
+        <f t="shared" ref="C95:C104" si="5">VLOOKUP(B95,$B$58:$D$68,2,0)</f>
         <v>34.598979030000002</v>
       </c>
       <c r="D95" s="2">
@@ -17004,21 +21156,30 @@
       <c r="F95" s="5">
         <v>371.7</v>
       </c>
-      <c r="G95" s="2">
-        <f t="shared" ref="G95:G104" si="4">D95-E95</f>
+      <c r="G95" s="5">
+        <v>182.4</v>
+      </c>
+      <c r="H95" s="5">
+        <v>225.73</v>
+      </c>
+      <c r="I95" s="5">
+        <v>235.86</v>
+      </c>
+      <c r="J95" s="2">
+        <f t="shared" ref="J95:J104" si="6">D95-E95</f>
         <v>78.009999999999991</v>
       </c>
-      <c r="H95" s="4">
-        <f t="shared" ref="H95:H104" si="5">IF(F95&lt;&gt;"",F95-E95, 0)</f>
+      <c r="K95" s="4">
+        <f t="shared" ref="K95:K104" si="7">IF(F95&lt;&gt;"",F95-E95, 0)</f>
         <v>88.70999999999998</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>17</v>
       </c>
       <c r="C96" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3.2566599309999997</v>
       </c>
       <c r="D96" s="2">
@@ -17030,21 +21191,30 @@
       <c r="F96" s="5">
         <v>307.8</v>
       </c>
-      <c r="G96" s="2">
-        <f t="shared" si="4"/>
+      <c r="G96" s="5">
+        <v>189.68</v>
+      </c>
+      <c r="H96" s="5">
+        <v>204.3</v>
+      </c>
+      <c r="I96" s="5">
+        <v>201.6</v>
+      </c>
+      <c r="J96" s="2">
+        <f t="shared" si="6"/>
         <v>80.079999999999984</v>
       </c>
-      <c r="H96" s="4">
-        <f t="shared" si="5"/>
+      <c r="K96" s="4">
+        <f t="shared" si="7"/>
         <v>36.879999999999995</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
         <v>19</v>
       </c>
       <c r="C97" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7.76826843</v>
       </c>
       <c r="D97" s="2">
@@ -17056,16 +21226,25 @@
       <c r="F97" s="5">
         <v>187.85</v>
       </c>
-      <c r="G97" s="2">
-        <f t="shared" si="4"/>
+      <c r="G97" s="5">
+        <v>239.58</v>
+      </c>
+      <c r="H97" s="5">
+        <v>248.8</v>
+      </c>
+      <c r="I97" s="5">
+        <v>236.07</v>
+      </c>
+      <c r="J97" s="2">
+        <f t="shared" si="6"/>
         <v>38.580000000000013</v>
       </c>
-      <c r="H97" s="4">
-        <f t="shared" si="5"/>
+      <c r="K97" s="4">
+        <f t="shared" si="7"/>
         <v>20.430000000000007</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>27</v>
       </c>
@@ -17073,7 +21252,7 @@
         <v>21</v>
       </c>
       <c r="C98" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>66.19802722</v>
       </c>
       <c r="D98" s="2">
@@ -17085,21 +21264,28 @@
       <c r="F98" s="7">
         <v>208.06</v>
       </c>
-      <c r="G98" s="2">
-        <f t="shared" si="4"/>
+      <c r="G98" s="7">
+        <v>241.3</v>
+      </c>
+      <c r="H98" s="7">
+        <v>234.77</v>
+      </c>
+      <c r="I98" s="7"/>
+      <c r="J98" s="2">
+        <f t="shared" si="6"/>
         <v>-8.2199999999999989</v>
       </c>
-      <c r="H98" s="4">
-        <f t="shared" si="5"/>
+      <c r="K98" s="4">
+        <f t="shared" si="7"/>
         <v>12.939999999999998</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>13.486557269999999</v>
       </c>
       <c r="D99" s="2">
@@ -17111,21 +21297,28 @@
       <c r="F99" s="5">
         <v>223.67</v>
       </c>
-      <c r="G99" s="2">
-        <f t="shared" si="4"/>
+      <c r="G99" s="5">
+        <v>260.10000000000002</v>
+      </c>
+      <c r="H99" s="5">
+        <v>287.91000000000003</v>
+      </c>
+      <c r="I99" s="5"/>
+      <c r="J99" s="2">
+        <f t="shared" si="6"/>
         <v>-65.81</v>
       </c>
-      <c r="H99" s="4">
-        <f t="shared" si="5"/>
+      <c r="K99" s="4">
+        <f t="shared" si="7"/>
         <v>-40.140000000000015</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>14.58223203</v>
       </c>
       <c r="D100" s="2">
@@ -17137,21 +21330,30 @@
       <c r="F100" s="5">
         <v>345.61</v>
       </c>
-      <c r="G100" s="2">
-        <f t="shared" si="4"/>
+      <c r="G100" s="5">
+        <v>218.71</v>
+      </c>
+      <c r="H100" s="5">
+        <v>240.87</v>
+      </c>
+      <c r="I100" s="5">
+        <v>250.71</v>
+      </c>
+      <c r="J100" s="2">
+        <f t="shared" si="6"/>
         <v>-41.259999999999991</v>
       </c>
-      <c r="H100" s="4">
-        <f t="shared" si="5"/>
+      <c r="K100" s="4">
+        <f t="shared" si="7"/>
         <v>-32.649999999999977</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
         <v>8</v>
       </c>
       <c r="C101" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>61.985700940000001</v>
       </c>
       <c r="D101" s="2">
@@ -17163,16 +21365,25 @@
       <c r="F101" s="5">
         <v>223.14</v>
       </c>
-      <c r="G101" s="2">
-        <f t="shared" si="4"/>
+      <c r="G101" s="5">
+        <v>200.8</v>
+      </c>
+      <c r="H101" s="5">
+        <v>201.04</v>
+      </c>
+      <c r="I101" s="5">
+        <v>201.35</v>
+      </c>
+      <c r="J101" s="2">
+        <f t="shared" si="6"/>
         <v>-37.349999999999994</v>
       </c>
-      <c r="H101" s="4">
-        <f t="shared" si="5"/>
+      <c r="K101" s="4">
+        <f t="shared" si="7"/>
         <v>-3.8100000000000023</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>29</v>
       </c>
@@ -17180,7 +21391,7 @@
         <v>9</v>
       </c>
       <c r="C102" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>38.822217160000001</v>
       </c>
       <c r="D102" s="2">
@@ -17192,21 +21403,30 @@
       <c r="F102" s="5">
         <v>274.22000000000003</v>
       </c>
-      <c r="G102" s="2">
-        <f t="shared" si="4"/>
+      <c r="G102" s="5">
+        <v>167.77</v>
+      </c>
+      <c r="H102" s="5">
+        <v>177.4</v>
+      </c>
+      <c r="I102" s="5">
+        <v>185.46</v>
+      </c>
+      <c r="J102" s="2">
+        <f t="shared" si="6"/>
         <v>1.4599999999999795</v>
       </c>
-      <c r="H102" s="4">
-        <f t="shared" si="5"/>
+      <c r="K102" s="4">
+        <f t="shared" si="7"/>
         <v>12.680000000000007</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
         <v>10</v>
       </c>
       <c r="C103" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>40.82876701</v>
       </c>
       <c r="D103" s="2">
@@ -17218,21 +21438,30 @@
       <c r="F103" s="5">
         <v>170.05</v>
       </c>
-      <c r="G103" s="2">
-        <f t="shared" si="4"/>
+      <c r="G103" s="5">
+        <v>224.26</v>
+      </c>
+      <c r="H103" s="5">
+        <v>225.75</v>
+      </c>
+      <c r="I103" s="5">
+        <v>217.3</v>
+      </c>
+      <c r="J103" s="2">
+        <f t="shared" si="6"/>
         <v>-44.22999999999999</v>
       </c>
-      <c r="H103" s="4">
-        <f t="shared" si="5"/>
+      <c r="K103" s="4">
+        <f t="shared" si="7"/>
         <v>-35.679999999999978</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>11</v>
       </c>
       <c r="C104" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7.1747951170000004</v>
       </c>
       <c r="D104" s="2">
@@ -17244,33 +21473,57 @@
       <c r="F104" s="5">
         <v>201.57</v>
       </c>
-      <c r="G104" s="2">
-        <f t="shared" si="4"/>
+      <c r="G104" s="5">
+        <v>317.08</v>
+      </c>
+      <c r="H104" s="5">
+        <v>324.5</v>
+      </c>
+      <c r="I104" s="5">
+        <v>304.33999999999997</v>
+      </c>
+      <c r="J104" s="2">
+        <f t="shared" si="6"/>
         <v>-42.75</v>
       </c>
-      <c r="H104" s="4">
-        <f t="shared" si="5"/>
+      <c r="K104" s="4">
+        <f t="shared" si="7"/>
         <v>-7.6800000000000068</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D105" s="2"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B106" t="s">
+        <v>37</v>
+      </c>
       <c r="D106" s="4">
-        <f>AVERAGE(D94:D104)</f>
+        <f t="shared" ref="D106:I106" si="8">AVERAGE(D94:D104)</f>
         <v>251.5</v>
       </c>
       <c r="E106" s="4">
-        <f>AVERAGE(E94:E104)</f>
+        <f t="shared" si="8"/>
         <v>252.95363636363638</v>
       </c>
       <c r="F106" s="4">
-        <f>AVERAGE(F94:F104)</f>
+        <f t="shared" si="8"/>
         <v>259.02454545454543</v>
       </c>
+      <c r="G106" s="4">
+        <f t="shared" si="8"/>
+        <v>221.11636363636364</v>
+      </c>
+      <c r="H106" s="4">
+        <f t="shared" si="8"/>
+        <v>234.06727272727275</v>
+      </c>
+      <c r="I106" s="4">
+        <f t="shared" si="8"/>
+        <v>226.71777777777777</v>
+      </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D107" s="4">
         <f>_xlfn.STDEV.P(D94:D104)/SQRT(COUNT(D94:D104))</f>
         <v>23.447765052354431</v>
@@ -17283,10 +21536,19 @@
         <f>_xlfn.STDEV.P(F94:F104)/SQRT(COUNT(F94:F104))</f>
         <v>20.345138894441369</v>
       </c>
+      <c r="G107" s="4">
+        <f>_xlfn.STDEV.P(G94:G104)/SQRT(COUNT(G94:G104))</f>
+        <v>12.254107375008044</v>
+      </c>
+      <c r="H107" s="4">
+        <f>_xlfn.STDEV.P(H94:H104)/SQRT(COUNT(H94:H104))</f>
+        <v>12.057607597558871</v>
+      </c>
+      <c r="I107" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A45:G45" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A46:G54">
+  <autoFilter ref="A45:J45" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A46:J54">
       <sortCondition ref="D45"/>
     </sortState>
   </autoFilter>

--- a/Results/Summary.xlsx
+++ b/Results/Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://biu365-my.sharepoint.com/personal/samoily_biu_ac_il/Documents/Academic/Postdoc/Multiplexed analyses/IMC/Results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="306" documentId="11_F25DC773A252ABDACC1048A339584C225BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAD83873-CFA4-4F36-BF6E-3AA61EA55298}"/>
+  <xr:revisionPtr revIDLastSave="307" documentId="11_F25DC773A252ABDACC1048A339584C225BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{475E9150-94AB-4434-BE16-3236DB1F1EDF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="72">
   <si>
     <t>Dataset</t>
   </si>
@@ -249,6 +249,15 @@
   <si>
     <t>Str.</t>
   </si>
+  <si>
+    <t xml:space="preserve">cross-dataset generalisation from Jackson→Danenberg </t>
+  </si>
+  <si>
+    <t>Good (r &gt; 0.35): ERa, HER2, pan_cytokeratin, cd45, cytokeratin_8_18 — abundant, high-dynamic-range markers</t>
+  </si>
+  <si>
+    <t>Bad (r &lt; 0.2): cytokeratin_5, cd68, ki_67, cd20, cd3 — sparse or weakly expressed markers dominated by background</t>
+  </si>
 </sst>
 </file>
 
@@ -478,7 +487,7 @@
                     <c:v>Immune</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Mean</c:v>
+                    <c:v>Avg.</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -619,7 +628,7 @@
                     <c:v>Immune</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Mean</c:v>
+                    <c:v>Avg.</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -759,7 +768,7 @@
                     <c:v>Immune</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>Mean</c:v>
+                    <c:v>Avg.</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -1011,8 +1020,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.78117907648728124"/>
-          <c:y val="3.2985564304461944E-2"/>
+          <c:x val="0.77275797778918642"/>
+          <c:y val="7.0001664997418708E-2"/>
           <c:w val="0.20496904500264984"/>
           <c:h val="0.22630521042179083"/>
         </c:manualLayout>
@@ -1023,7 +1032,9 @@
           <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
         <a:ln>
-          <a:noFill/>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -6155,51 +6166,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.48223007270491491"/>
-          <c:y val="7.0001664997418708E-2"/>
-          <c:w val="0.20496904500264984"/>
-          <c:h val="0.19391609214540201"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:solidFill>
-          <a:sysClr val="window" lastClr="FFFFFF"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="LID4096"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -18239,16 +18205,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>251810</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>136854</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>48963</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66299</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>207983</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>89792</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>5137</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>19237</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -18278,15 +18244,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>27371</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>65689</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>563803</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>139059</xdr:rowOff>
+      <xdr:colOff>591174</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>18628</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -19226,7 +19192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CB3BE29-5887-47D2-B6DB-21DD0F45101E}">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
@@ -19309,6 +19275,9 @@
       <c r="E4">
         <v>225.7</v>
       </c>
+      <c r="H4" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
@@ -19482,12 +19451,12 @@
         <v>12.646675975256962</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>1</v>
       </c>
@@ -19501,7 +19470,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -19518,7 +19487,7 @@
         <v>0.63600000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>10</v>
       </c>
@@ -19532,7 +19501,7 @@
         <v>0.41199999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>44</v>
       </c>
@@ -19546,7 +19515,7 @@
         <v>0.183</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -19562,8 +19531,11 @@
       <c r="E23" s="4">
         <v>0.38900000000000001</v>
       </c>
+      <c r="R23" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>61</v>
       </c>
@@ -19576,8 +19548,11 @@
       <c r="E24" s="4">
         <v>0.124</v>
       </c>
+      <c r="R24" t="s">
+        <v>71</v>
+      </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>62</v>
       </c>
@@ -19591,7 +19566,7 @@
         <v>0.253</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>68</v>
       </c>
@@ -19608,7 +19583,7 @@
         <v>0.39100000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -19625,7 +19600,7 @@
         <v>0.437</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>45</v>
       </c>
@@ -19639,7 +19614,7 @@
         <v>0.253</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>46</v>
       </c>
@@ -19653,7 +19628,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>48</v>
       </c>
@@ -19667,9 +19642,9 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>67</v>
@@ -19687,7 +19662,7 @@
         <v>0.30490909090909091</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>55</v>
       </c>

--- a/Results/Summary.xlsx
+++ b/Results/Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://biu365-my.sharepoint.com/personal/samoily_biu_ac_il/Documents/Academic/Postdoc/Multiplexed analyses/IMC/Results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="307" documentId="11_F25DC773A252ABDACC1048A339584C225BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{475E9150-94AB-4434-BE16-3236DB1F1EDF}"/>
+  <xr:revisionPtr revIDLastSave="308" documentId="11_F25DC773A252ABDACC1048A339584C225BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55F4EEC6-A72E-4AB7-BEB7-71FF0A48E79E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -250,13 +250,13 @@
     <t>Str.</t>
   </si>
   <si>
-    <t xml:space="preserve">cross-dataset generalisation from Jackson→Danenberg </t>
-  </si>
-  <si>
     <t>Good (r &gt; 0.35): ERa, HER2, pan_cytokeratin, cd45, cytokeratin_8_18 — abundant, high-dynamic-range markers</t>
   </si>
   <si>
     <t>Bad (r &lt; 0.2): cytokeratin_5, cd68, ki_67, cd20, cd3 — sparse or weakly expressed markers dominated by background</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-dataset generalisation from Jackson→Danenberg </t>
   </si>
 </sst>
 </file>
@@ -19276,7 +19276,7 @@
         <v>225.7</v>
       </c>
       <c r="H4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -19532,7 +19532,7 @@
         <v>0.38900000000000001</v>
       </c>
       <c r="R23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
@@ -19549,7 +19549,7 @@
         <v>0.124</v>
       </c>
       <c r="R24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
@@ -21004,7 +21004,7 @@
         <v>31</v>
       </c>
       <c r="D90" s="1">
-        <f t="shared" ref="D90:K90" si="3">AVERAGE(D77:D88)</f>
+        <f t="shared" ref="D90:J90" si="3">AVERAGE(D77:D88)</f>
         <v>0.28969090909090911</v>
       </c>
       <c r="E90" s="1">
